--- a/word-lists/100-wordlist-Finnish.xlsx
+++ b/word-lists/100-wordlist-Finnish.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A819B6F-B4C4-413B-A934-D6D1F57B9F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02BBC1E0-345A-475B-9736-0DF0081F6708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{5DDCD74B-108E-4832-A76F-CFE07C428A11}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{0EE85467-4D5C-4678-903B-8ADDC89AE2FF}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Finnish" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
     <t>yhdessä</t>
   </si>
   <si>
-    <t>kävelyllä</t>
+    <t>kävellä</t>
   </si>
   <si>
     <t>hetki</t>
@@ -204,7 +204,7 @@
     <t>koti</t>
   </si>
   <si>
-    <t>kävellä</t>
+    <t>oppia</t>
   </si>
   <si>
     <t>uusi</t>
@@ -321,10 +321,10 @@
     <t>erilainen</t>
   </si>
   <si>
-    <t>tärkeä</t>
-  </si>
-  <si>
-    <t>tieto</t>
+    <t>ymmärtäminen</t>
+  </si>
+  <si>
+    <t>tärkeintä</t>
   </si>
   <si>
     <t>hallitus</t>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E79D3D-6744-4225-8CB0-93DA4E20212E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6DDB4E-B259-45F4-8D16-BC9499872485}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1744,7 +1744,7 @@
         <v>51</v>
       </c>
       <c r="C50">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
